--- a/resultados/arapoti/erros_varredura.xlsx
+++ b/resultados/arapoti/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F508"/>
+  <dimension ref="A1:F521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14644,6 +14644,370 @@
         </is>
       </c>
     </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Atos-do-Presidente/0/1/0/24396</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>0</v>
+      </c>
+      <c r="E509" t="n">
+        <v>6</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2026-08-01 13:16:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Atos-do-Presidente/2022/1/0/20460</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>0</v>
+      </c>
+      <c r="E510" t="n">
+        <v>6</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2026-08-01 13:48:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/softcam/digital_extrato_print_pdf.php?chave=2607231105277E42</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>0</v>
+      </c>
+      <c r="E511" t="n">
+        <v>6</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:27:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/softcam/digital_extrato_print_pdf.php?chave=26030913125345E32</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>0</v>
+      </c>
+      <c r="E512" t="n">
+        <v>6</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:36:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Portarias/2025/1/0/23232</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>0</v>
+      </c>
+      <c r="E513" t="n">
+        <v>6</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2026-08-01 14:53:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Portarias/2025/1/0/22999</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>0</v>
+      </c>
+      <c r="E514" t="n">
+        <v>6</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:08:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Portarias/2022/1/0/20223</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>0</v>
+      </c>
+      <c r="E515" t="n">
+        <v>6</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:26:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Portarias/2021/1/0/17565</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>0</v>
+      </c>
+      <c r="E516" t="n">
+        <v>6</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:35:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Portarias/2020/1/0/17523</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>0</v>
+      </c>
+      <c r="E517" t="n">
+        <v>6</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-08-01 16:06:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Portarias/2020/1/0/17293</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>0</v>
+      </c>
+      <c r="E518" t="n">
+        <v>6</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-08-01 16:22:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/proposicoes/Portarias/2013/1/0/8343</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>0</v>
+      </c>
+      <c r="E519" t="n">
+        <v>6</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-08-01 16:54:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/imprensa/noticias/0/5/0/2184</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>0</v>
+      </c>
+      <c r="E520" t="n">
+        <v>6</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-08-01 17:38:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>arapoti</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://www.cmarapoti.pr.gov.br/tvcamara/videos/TV-Camara/4/2402/sessao_ordinaria</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>0</v>
+      </c>
+      <c r="E521" t="n">
+        <v>6</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-08-01 18:23:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
